--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R4" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>92546</v>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R5" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B4" t="n">
-        <v>92558</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R4" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>92560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R5" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125220967</v>
       </c>
       <c r="B5" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R4" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>92562</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R5" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>92564</v>
+        <v>92568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B4" t="n">
-        <v>92568</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R4" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>92568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R5" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>92568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R4" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>92568</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R5" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>92568</v>
+        <v>92571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B4" t="n">
-        <v>92571</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R4" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>92571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R5" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125220968</v>
+        <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>92571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671622</v>
+        <v>671648</v>
       </c>
       <c r="R4" t="n">
-        <v>7170040</v>
+        <v>7170066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125220967</v>
+        <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>92571</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671648</v>
+        <v>671622</v>
       </c>
       <c r="R5" t="n">
-        <v>7170066</v>
+        <v>7170040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125220970</v>
       </c>
       <c r="B2" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,11 +788,11 @@
         <v>125220969</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -898,7 +898,7 @@
         <v>125220967</v>
       </c>
       <c r="B4" t="n">
-        <v>92571</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125220968</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27068-2025 artfynd.xlsx
+++ b/artfynd/A 27068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125220970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125220969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125220967</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125220968</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>